--- a/gte/nodes/LPC/compressor_stage_2_blade_rotor_coordinates_foil.xlsx
+++ b/gte/nodes/LPC/compressor_stage_2_blade_rotor_coordinates_foil.xlsx
@@ -357,7 +357,7 @@
         <v>0.0016587594588024957</v>
       </c>
       <c r="B2">
-        <v>0.0019521402043635476</v>
+        <v>0.0019473196703446377</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -365,7 +365,7 @@
         <v>0.0033175189176049913</v>
       </c>
       <c r="B3">
-        <v>0.0030976242500014022</v>
+        <v>0.0030883573800384247</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -373,7 +373,7 @@
         <v>0.0049762783764074874</v>
       </c>
       <c r="B4">
-        <v>0.004094498005159721</v>
+        <v>0.0040811339045111646</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -381,7 +381,7 @@
         <v>0.0066350378352099827</v>
       </c>
       <c r="B5">
-        <v>0.0049803197430906259</v>
+        <v>0.0049631853953995457</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -389,7 +389,7 @@
         <v>0.0082937972940124779</v>
       </c>
       <c r="B6">
-        <v>0.0057709260848394913</v>
+        <v>0.0057503288208406791</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -397,7 +397,7 @@
         <v>0.0099525567528149748</v>
       </c>
       <c r="B7">
-        <v>0.0064756532032038761</v>
+        <v>0.0064518834536896877</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -405,7 +405,7 @@
         <v>0.01161131621161747</v>
       </c>
       <c r="B8">
-        <v>0.007100284969605802</v>
+        <v>0.0070736174891722174</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -413,7 +413,7 @@
         <v>0.013270075670419965</v>
       </c>
       <c r="B9">
-        <v>0.0076533135490339148</v>
+        <v>0.007624009889335065</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -421,7 +421,7 @@
         <v>0.014928835129222461</v>
       </c>
       <c r="B10">
-        <v>0.008143805157009066</v>
+        <v>0.0081121147516233123</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -429,7 +429,7 @@
         <v>0.016587594588024956</v>
       </c>
       <c r="B11">
-        <v>0.0085804139176143129</v>
+        <v>0.00854657594825403</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -437,7 +437,7 @@
         <v>0.018246354046827454</v>
       </c>
       <c r="B12">
-        <v>0.0089679743099597611</v>
+        <v>0.0089322185594057947</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -445,7 +445,7 @@
         <v>0.01990511350562995</v>
       </c>
       <c r="B13">
-        <v>0.009296454324701468</v>
+        <v>0.0092590027223311763</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -453,7 +453,7 @@
         <v>0.021563872964432445</v>
       </c>
       <c r="B14">
-        <v>0.0095599903683448433</v>
+        <v>0.0095210577229374281</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -461,7 +461,7 @@
         <v>0.02322263242323494</v>
       </c>
       <c r="B15">
-        <v>0.0097842589992467414</v>
+        <v>0.00974405438467649</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -469,7 +469,7 @@
         <v>0.024881391882037432</v>
       </c>
       <c r="B16">
-        <v>0.0099928073521064528</v>
+        <v>0.00995153467528699</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -477,7 +477,7 @@
         <v>0.026540151340839931</v>
       </c>
       <c r="B17">
-        <v>0.010169124715141583</v>
+        <v>0.01012698360210954</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -485,7 +485,7 @@
         <v>0.028198910799642429</v>
       </c>
       <c r="B18">
-        <v>0.010291782835145936</v>
+        <v>0.010248969274985321</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -493,7 +493,7 @@
         <v>0.029857670258444921</v>
       </c>
       <c r="B19">
-        <v>0.010359741139699808</v>
+        <v>0.010316449174155746</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -501,7 +501,7 @@
         <v>0.03151642971724742</v>
       </c>
       <c r="B20">
-        <v>0.010377055976580106</v>
+        <v>0.010333478122462289</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -509,7 +509,7 @@
         <v>0.033175189176049912</v>
       </c>
       <c r="B21">
-        <v>0.010347783693563746</v>
+        <v>0.010304110942746419</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -517,7 +517,7 @@
         <v>0.03483394863485241</v>
       </c>
       <c r="B22">
-        <v>0.01027524531476931</v>
+        <v>0.010231667631137371</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -525,7 +525,7 @@
         <v>0.036492708093654909</v>
       </c>
       <c r="B23">
-        <v>0.010159820569682064</v>
+        <v>0.010116528876915406</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -533,7 +533,7 @@
         <v>0.0381514675524574</v>
       </c>
       <c r="B24">
-        <v>0.010001153864128939</v>
+        <v>0.0099583405426485489</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -541,7 +541,7 @@
         <v>0.0398102270112599</v>
       </c>
       <c r="B25">
-        <v>0.0097988896039368657</v>
+        <v>0.0097567484909048229</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -549,7 +549,7 @@
         <v>0.041468986470062391</v>
       </c>
       <c r="B26">
-        <v>0.0095525262709177158</v>
+        <v>0.0095112531785250861</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -557,7 +557,7 @@
         <v>0.04312774592886489</v>
       </c>
       <c r="B27">
-        <v>0.0092609786508230773</v>
+        <v>0.0092207734394415368</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -565,7 +565,7 @@
         <v>0.044786505387667382</v>
       </c>
       <c r="B28">
-        <v>0.00892301560538948</v>
+        <v>0.0088840827018592146</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -573,7 +573,7 @@
         <v>0.04644526484646988</v>
       </c>
       <c r="B29">
-        <v>0.0085374059963534438</v>
+        <v>0.0084999543939831522</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -581,7 +581,7 @@
         <v>0.048104024305272379</v>
       </c>
       <c r="B30">
-        <v>0.0081034105285473224</v>
+        <v>0.0080676544351700637</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -589,7 +589,7 @@
         <v>0.049762783764074864</v>
       </c>
       <c r="B31">
-        <v>0.0076222572791867643</v>
+        <v>0.0075884187093833537</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -597,7 +597,7 @@
         <v>0.051421543222877363</v>
       </c>
       <c r="B32">
-        <v>0.0070956661685832381</v>
+        <v>0.0070639755917380944</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -605,7 +605,7 @@
         <v>0.053080302681679861</v>
       </c>
       <c r="B33">
-        <v>0.0065253571170482165</v>
+        <v>0.0064960534573493666</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -613,7 +613,7 @@
         <v>0.05473906214048236</v>
       </c>
       <c r="B34">
-        <v>0.005912154459167855</v>
+        <v>0.0058854860847549007</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -621,7 +621,7 @@
         <v>0.056397821599284859</v>
       </c>
       <c r="B35">
-        <v>0.0052533001866270322</v>
+        <v>0.0052295288661830461</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -629,7 +629,7 @@
         <v>0.058056581058087343</v>
       </c>
       <c r="B36">
-        <v>0.0045451407053853175</v>
+        <v>0.0045245425972848087</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -637,7 +637,7 @@
         <v>0.059715340516889842</v>
       </c>
       <c r="B37">
-        <v>0.0037840224214022657</v>
+        <v>0.0037668880737111851</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -645,7 +645,7 @@
         <v>0.061374099975692341</v>
       </c>
       <c r="B38">
-        <v>0.0029641528441179425</v>
+        <v>0.0029507885388368868</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -653,7 +653,7 @@
         <v>0.06303285943449484</v>
       </c>
       <c r="B39">
-        <v>0.0020711838968944141</v>
+        <v>0.0020619170269314366</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -661,7 +661,7 @@
         <v>0.064691618893297331</v>
       </c>
       <c r="B40">
-        <v>0.0010886286065742432</v>
+        <v>0.0010838090199880635</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -685,7 +685,7 @@
         <v>0.064691618893297331</v>
       </c>
       <c r="B43">
-        <v>0.00036061939991029711</v>
+        <v>0.00035579981332411727</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -693,7 +693,7 @@
         <v>0.06303285943449484</v>
       </c>
       <c r="B44">
-        <v>0.000740195307151294</v>
+        <v>0.00073092843718831663</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -701,7 +701,7 @@
         <v>0.061374099975692341</v>
       </c>
       <c r="B45">
-        <v>0.0011244024085556306</v>
+        <v>0.0011110381032745742</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -709,7 +709,7 @@
         <v>0.059715340516889842</v>
       </c>
       <c r="B46">
-        <v>0.0014989153909559477</v>
+        <v>0.0014817810432648675</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -717,7 +717,7 @@
         <v>0.058056581058087343</v>
       </c>
       <c r="B47">
-        <v>0.0018514380924943975</v>
+        <v>0.0018308399843938886</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -725,7 +725,7 @@
         <v>0.056397821599284859</v>
       </c>
       <c r="B48">
-        <v>0.0021777909565511727</v>
+        <v>0.0021540196361071857</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -733,7 +733,7 @@
         <v>0.05473906214048236</v>
       </c>
       <c r="B49">
-        <v>0.0024758235778159815</v>
+        <v>0.0024491552034030272</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -741,7 +741,7 @@
         <v>0.053080302681679861</v>
       </c>
       <c r="B50">
-        <v>0.0027433855509785268</v>
+        <v>0.0027140818912796765</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -749,7 +749,7 @@
         <v>0.051421543222877363</v>
       </c>
       <c r="B51">
-        <v>0.00297912986938216</v>
+        <v>0.0029474392925370177</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -757,7 +757,7 @@
         <v>0.049762783764074864</v>
       </c>
       <c r="B52">
-        <v>0.0031849231209848216</v>
+        <v>0.0031510845511814115</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -765,7 +765,7 @@
         <v>0.048104024305272379</v>
       </c>
       <c r="B53">
-        <v>0.0033634352923980959</v>
+        <v>0.0033276791990208385</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -773,7 +773,7 @@
         <v>0.04644526484646988</v>
       </c>
       <c r="B54">
-        <v>0.0035173363702335715</v>
+        <v>0.0034798847678632811</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -781,7 +781,7 @@
         <v>0.044786505387667382</v>
       </c>
       <c r="B55">
-        <v>0.0036487352866201319</v>
+        <v>0.0036098023830898667</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -789,7 +789,7 @@
         <v>0.04312774592886489</v>
       </c>
       <c r="B56">
-        <v>0.0037574967557558571</v>
+        <v>0.0037172915443743158</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -797,7 +797,7 @@
         <v>0.041468986470062391</v>
       </c>
       <c r="B57">
-        <v>0.0038429244373561263</v>
+        <v>0.0038016513449634962</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -805,7 +805,7 @@
         <v>0.0398102270112599</v>
       </c>
       <c r="B58">
-        <v>0.0039043219911363185</v>
+        <v>0.0038621808781042748</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -813,7 +813,7 @@
         <v>0.0381514675524574</v>
       </c>
       <c r="B59">
-        <v>0.0039410789644760283</v>
+        <v>0.00389826564299564</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -821,7 +821,7 @@
         <v>0.036492708093654909</v>
       </c>
       <c r="B60">
-        <v>0.0039529284554117158</v>
+        <v>0.0039096367626450584</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -829,7 +829,7 @@
         <v>0.03483394863485241</v>
       </c>
       <c r="B61">
-        <v>0.0039396894496440561</v>
+        <v>0.003896111766012116</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -837,7 +837,7 @@
         <v>0.033175189176049912</v>
       </c>
       <c r="B62">
-        <v>0.0039011809328737259</v>
+        <v>0.003857508182056399</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -845,7 +845,7 @@
         <v>0.03151642971724742</v>
       </c>
       <c r="B63">
-        <v>0.0038378977565850323</v>
+        <v>0.0037943199024672142</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -853,7 +853,7 @@
         <v>0.029857670258444921</v>
       </c>
       <c r="B64">
-        <v>0.0037530382353968051</v>
+        <v>0.0037097462698527438</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -861,7 +861,7 @@
         <v>0.028198910799642429</v>
       </c>
       <c r="B65">
-        <v>0.0036504765497115074</v>
+        <v>0.0036076629895508906</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -869,7 +869,7 @@
         <v>0.026540151340839931</v>
       </c>
       <c r="B66">
-        <v>0.0035340868799316012</v>
+        <v>0.0034919457668995575</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -877,7 +877,7 @@
         <v>0.024881391882037432</v>
       </c>
       <c r="B67">
-        <v>0.0034025970737882527</v>
+        <v>0.0033613243969687892</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -885,7 +885,7 @@
         <v>0.02322263242323494</v>
       </c>
       <c r="B68">
-        <v>0.0032341496483274459</v>
+        <v>0.0031939450337571959</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -893,7 +893,7 @@
         <v>0.021563872964432445</v>
       </c>
       <c r="B69">
-        <v>0.0030117309585405354</v>
+        <v>0.0029727983131331193</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -901,7 +901,7 @@
         <v>0.01990511350562995</v>
       </c>
       <c r="B70">
-        <v>0.0027582880418855504</v>
+        <v>0.00272083643951526</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -909,7 +909,7 @@
         <v>0.018246354046827454</v>
       </c>
       <c r="B71">
-        <v>0.0024988360222305732</v>
+        <v>0.0024630802716766073</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -917,7 +917,7 @@
         <v>0.016587594588024956</v>
       </c>
       <c r="B72">
-        <v>0.0022267016866172342</v>
+        <v>0.0021928637172569511</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -925,7 +925,7 @@
         <v>0.014928835129222461</v>
       </c>
       <c r="B73">
-        <v>0.0019309677678977114</v>
+        <v>0.0018992773625119573</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -933,7 +933,7 @@
         <v>0.013270075670419965</v>
       </c>
       <c r="B74">
-        <v>0.0016154291189928295</v>
+        <v>0.0015861254592939797</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -941,7 +941,7 @@
         <v>0.01161131621161747</v>
       </c>
       <c r="B75">
-        <v>0.0012876176930818554</v>
+        <v>0.0012609502126482706</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -949,7 +949,7 @@
         <v>0.0099525567528149748</v>
       </c>
       <c r="B76">
-        <v>0.00095530172430917046</v>
+        <v>0.00093153197479498224</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -957,7 +957,7 @@
         <v>0.0082937972940124779</v>
       </c>
       <c r="B77">
-        <v>0.00062557760375372</v>
+        <v>0.00060498033975490756</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -965,7 +965,7 @@
         <v>0.0066350378352099827</v>
       </c>
       <c r="B78">
-        <v>0.000302618069267588</v>
+        <v>0.0002854837215765078</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -973,7 +973,7 @@
         <v>0.0049762783764074874</v>
       </c>
       <c r="B79">
-        <v>-5.9553770000480795E-06</v>
+        <v>-1.9319477648604655E-05</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -981,7 +981,7 @@
         <v>0.0033175189176049913</v>
       </c>
       <c r="B80">
-        <v>-0.00028624504595568812</v>
+        <v>-0.00029551191591866549</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -989,7 +989,7 @@
         <v>0.0016587594588024957</v>
       </c>
       <c r="B81">
-        <v>-0.00050282379466414591</v>
+        <v>-0.00050764432868305562</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1015,7 +1015,7 @@
         <v>0</v>
       </c>
       <c r="B1">
-        <v>-6.8406106131357487E-17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -1023,7 +1023,7 @@
         <v>0.0019254607130190513</v>
       </c>
       <c r="B2">
-        <v>0.00086014279936003708</v>
+        <v>0.0008674809313830254</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1031,7 +1031,7 @@
         <v>0.0038509214260381026</v>
       </c>
       <c r="B3">
-        <v>0.001350806456215899</v>
+        <v>0.0013650821644297549</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1039,7 +1039,7 @@
         <v>0.0057763821390571539</v>
       </c>
       <c r="B4">
-        <v>0.0017770341326359253</v>
+        <v>0.0017978508113103708</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1047,7 +1047,7 @@
         <v>0.0077018428520762051</v>
       </c>
       <c r="B5">
-        <v>0.0021558171015615209</v>
+        <v>0.0021827818476449104</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1055,7 +1055,7 @@
         <v>0.0096273035650952556</v>
       </c>
       <c r="B6">
-        <v>0.002494102842039961</v>
+        <v>0.0025268262270055817</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1063,7 +1063,7 @@
         <v>0.011552764278114308</v>
       </c>
       <c r="B7">
-        <v>0.0027958691170309742</v>
+        <v>0.0028339648977290638</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1071,7 +1071,7 @@
         <v>0.01347822499113336</v>
       </c>
       <c r="B8">
-        <v>0.0030634665828735857</v>
+        <v>0.0031065515586625944</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1079,7 +1079,7 @@
         <v>0.01540368570415241</v>
       </c>
       <c r="B9">
-        <v>0.003300549520969494</v>
+        <v>0.0033482432219421468</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1087,7 +1087,7 @@
         <v>0.017329146417171461</v>
       </c>
       <c r="B10">
-        <v>0.0035110595770544259</v>
+        <v>0.0035629841138938179</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1095,7 +1095,7 @@
         <v>0.019254607130190511</v>
       </c>
       <c r="B11">
-        <v>0.0036987842291375523</v>
+        <v>0.0037545640043154874</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1103,7 +1103,7 @@
         <v>0.021180067843209565</v>
       </c>
       <c r="B12">
-        <v>0.0038657548114954927</v>
+        <v>0.0039250163778409364</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1111,7 +1111,7 @@
         <v>0.023105528556228615</v>
       </c>
       <c r="B13">
-        <v>0.0040071322512012144</v>
+        <v>0.0040695040349757756</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1119,7 +1119,7 @@
         <v>0.025030989269247666</v>
       </c>
       <c r="B14">
-        <v>0.0041200286577698546</v>
+        <v>0.0041851408163086114</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1127,7 +1127,7 @@
         <v>0.02695644998226672</v>
       </c>
       <c r="B15">
-        <v>0.0042162312776889048</v>
+        <v>0.0042837154068882267</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1135,7 +1135,7 @@
         <v>0.028881910695285767</v>
       </c>
       <c r="B16">
-        <v>0.0043065512896738574</v>
+        <v>0.0043760403013640018</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1143,7 +1143,7 @@
         <v>0.030807371408304821</v>
       </c>
       <c r="B17">
-        <v>0.0043832204643798733</v>
+        <v>0.0044543483883275527</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1151,7 +1151,7 @@
         <v>0.032732832121323871</v>
       </c>
       <c r="B18">
-        <v>0.0044362023270464613</v>
+        <v>0.0045086041521919112</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1159,7 +1159,7 @@
         <v>0.034658292834342921</v>
       </c>
       <c r="B19">
-        <v>0.0044649668293108508</v>
+        <v>0.0045382780667135442</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1167,7 +1167,7 @@
         <v>0.036583753547361972</v>
       </c>
       <c r="B20">
-        <v>0.0044713605294097033</v>
+        <v>0.0045452171029847768</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1175,7 +1175,7 @@
         <v>0.038509214260381022</v>
       </c>
       <c r="B21">
-        <v>0.004457229985579677</v>
+        <v>0.0045312682320979318</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1183,7 +1183,7 @@
         <v>0.040434674973400073</v>
       </c>
       <c r="B22">
-        <v>0.0044240923622483322</v>
+        <v>0.0044979488963492863</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1191,7 +1191,7 @@
         <v>0.04236013568641913</v>
       </c>
       <c r="B23">
-        <v>0.0043721472486068233</v>
+        <v>0.0044454584228509264</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1199,7 +1199,7 @@
         <v>0.04428559639943818</v>
       </c>
       <c r="B24">
-        <v>0.0043012648400372047</v>
+        <v>0.0043736666099188888</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1207,7 +1207,7 @@
         <v>0.046211057112457231</v>
       </c>
       <c r="B25">
-        <v>0.0042113153319215313</v>
+        <v>0.0042824432558692107</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1215,7 +1215,7 @@
         <v>0.048136517825476274</v>
       </c>
       <c r="B26">
-        <v>0.0041021133838707764</v>
+        <v>0.0041716024920062109</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1223,7 +1223,7 @@
         <v>0.050061978538495332</v>
       </c>
       <c r="B27">
-        <v>0.00397325151241159</v>
+        <v>0.0040407357815873245</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1231,7 +1231,7 @@
         <v>0.051987439251514382</v>
       </c>
       <c r="B28">
-        <v>0.003824266698299543</v>
+        <v>0.0038893789208582709</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1239,7 +1239,7 @@
         <v>0.053912899964533439</v>
       </c>
       <c r="B29">
-        <v>0.0036546959222902055</v>
+        <v>0.0037170677060647662</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1247,7 +1247,7 @@
         <v>0.05583836067755249</v>
       </c>
       <c r="B30">
-        <v>0.0034643188431490988</v>
+        <v>0.0035235804752781594</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1255,7 +1255,7 @@
         <v>0.057763821390571533</v>
       </c>
       <c r="B31">
-        <v>0.0032538858316815585</v>
+        <v>0.0033096657338723225</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1263,7 +1263,7 @@
         <v>0.059689282103590584</v>
       </c>
       <c r="B32">
-        <v>0.0030243899367028678</v>
+        <v>0.0030763145290467571</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1271,7 +1271,7 @@
         <v>0.061614742816609641</v>
       </c>
       <c r="B33">
-        <v>0.0027768242070283118</v>
+        <v>0.0028245179080009647</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1279,7 +1279,7 @@
         <v>0.063540203529628692</v>
       </c>
       <c r="B34">
-        <v>0.0025117853833074373</v>
+        <v>0.0025548704606773802</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1287,7 +1287,7 @@
         <v>0.065465664242647742</v>
       </c>
       <c r="B35">
-        <v>0.0022282849735268282</v>
+        <v>0.0022663809479901609</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1295,7 +1295,7 @@
         <v>0.067391124955666792</v>
       </c>
       <c r="B36">
-        <v>0.0019249381775073302</v>
+        <v>0.0019576616735963968</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1303,7 +1303,7 @@
         <v>0.069316585668685843</v>
       </c>
       <c r="B37">
-        <v>0.0016003601950697851</v>
+        <v>0.0016273249411531746</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1311,7 +1311,7 @@
         <v>0.0712420463817049</v>
       </c>
       <c r="B38">
-        <v>0.0012521968448232245</v>
+        <v>0.0012730135308171545</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1319,7 +1319,7 @@
         <v>0.073167507094723944</v>
       </c>
       <c r="B39">
-        <v>0.00087421642052942165</v>
+        <v>0.0008884921287432776</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1327,7 +1327,7 @@
         <v>0.075092967807743</v>
       </c>
       <c r="B40">
-        <v>0.00045921783473833687</v>
+        <v>0.00046655589758605497</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -1335,7 +1335,7 @@
         <v>0.077018428520762044</v>
       </c>
       <c r="B41">
-        <v>-6.8272500455319684E-17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -1343,7 +1343,7 @@
         <v>0.077018428520762044</v>
       </c>
       <c r="B42">
-        <v>-6.8406106131357487E-17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -1351,7 +1351,7 @@
         <v>0.075092967807743</v>
       </c>
       <c r="B43">
-        <v>0.0001211933867187162</v>
+        <v>0.00012853144956643427</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -1359,7 +1359,7 @@
         <v>0.073167507094723944</v>
       </c>
       <c r="B44">
-        <v>0.00025622055007882817</v>
+        <v>0.00027049625829268407</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -1367,7 +1367,7 @@
         <v>0.0712420463817049</v>
       </c>
       <c r="B45">
-        <v>0.00039797601934145067</v>
+        <v>0.00041879270533538089</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -1375,7 +1375,7 @@
         <v>0.069316585668685843</v>
       </c>
       <c r="B46">
-        <v>0.0005393543237677674</v>
+        <v>0.00056631906985115678</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -1383,7 +1383,7 @@
         <v>0.067391124955666792</v>
       </c>
       <c r="B47">
-        <v>0.00067421589196929436</v>
+        <v>0.000706939388058361</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -1391,7 +1391,7 @@
         <v>0.065465664242647742</v>
       </c>
       <c r="B48">
-        <v>0.00080028474995887827</v>
+        <v>0.00083838072442221081</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -1399,7 +1399,7 @@
         <v>0.063540203529628692</v>
       </c>
       <c r="B49">
-        <v>0.00091625082309969958</v>
+        <v>0.00095933590046964239</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -1407,7 +1407,7 @@
         <v>0.061614742816609641</v>
       </c>
       <c r="B50">
-        <v>0.0010208040367549371</v>
+        <v>0.00106849773772759</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1415,7 +1415,7 @@
         <v>0.059689282103590584</v>
       </c>
       <c r="B51">
-        <v>0.0011130268693776806</v>
+        <v>0.0011649514617215698</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -1423,7 +1423,7 @@
         <v>0.057763821390571533</v>
       </c>
       <c r="B52">
-        <v>0.0011935720117806576</v>
+        <v>0.0012493519139714217</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -1431,7 +1431,7 @@
         <v>0.05583836067755249</v>
       </c>
       <c r="B53">
-        <v>0.0012634847078665057</v>
+        <v>0.0013227463399955661</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1439,7 +1439,7 @@
         <v>0.053912899964533439</v>
       </c>
       <c r="B54">
-        <v>0.0013238102015378634</v>
+        <v>0.0013861819853124245</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -1447,7 +1447,7 @@
         <v>0.051987439251514382</v>
       </c>
       <c r="B55">
-        <v>0.0013753475402266898</v>
+        <v>0.0014404597627854176</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1455,7 +1455,7 @@
         <v>0.050061978538495332</v>
       </c>
       <c r="B56">
-        <v>0.0014179109854822315</v>
+        <v>0.001485395254657966</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1463,7 +1463,7 @@
         <v>0.048136517825476274</v>
       </c>
       <c r="B57">
-        <v>0.0014510686023830562</v>
+        <v>0.00152055771051849</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1471,7 +1471,7 @@
         <v>0.046211057112457231</v>
       </c>
       <c r="B58">
-        <v>0.0014743884560077321</v>
+        <v>0.0015455163799554114</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1479,7 +1479,7 @@
         <v>0.04428559639943818</v>
       </c>
       <c r="B59">
-        <v>0.0014874907089384595</v>
+        <v>0.0015598924788201431</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1487,7 +1487,7 @@
         <v>0.04236013568641913</v>
       </c>
       <c r="B60">
-        <v>0.0014902039137719687</v>
+        <v>0.0015635150880160716</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1495,7 +1495,7 @@
         <v>0.040434674973400073</v>
       </c>
       <c r="B61">
-        <v>0.001482408720608622</v>
+        <v>0.0015562652547095762</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -1503,7 +1503,7 @@
         <v>0.038509214260381022</v>
       </c>
       <c r="B62">
-        <v>0.0014639857795487813</v>
+        <v>0.0015380240260670355</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -1511,7 +1511,7 @@
         <v>0.036583753547361972</v>
       </c>
       <c r="B63">
-        <v>0.0014351415810865227</v>
+        <v>0.0015089981546615957</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -1519,7 +1519,7 @@
         <v>0.034658292834342921</v>
       </c>
       <c r="B64">
-        <v>0.001397385977290776</v>
+        <v>0.0014706972146934691</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -1527,7 +1527,7 @@
         <v>0.032732832121323871</v>
       </c>
       <c r="B65">
-        <v>0.0013525546606241842</v>
+        <v>0.0014249564857696344</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -1535,7 +1535,7 @@
         <v>0.030807371408304821</v>
       </c>
       <c r="B66">
-        <v>0.001302483323549391</v>
+        <v>0.0013736112474970702</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -1543,7 +1543,7 @@
         <v>0.028881910695285767</v>
       </c>
       <c r="B67">
-        <v>0.0012466281853084496</v>
+        <v>0.0013161171969985942</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -1551,7 +1551,7 @@
         <v>0.02695644998226672</v>
       </c>
       <c r="B68">
-        <v>0.0011749275722610537</v>
+        <v>0.0012424117014603756</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -1559,7 +1559,7 @@
         <v>0.025030989269247666</v>
       </c>
       <c r="B69">
-        <v>0.0010795839048367499</v>
+        <v>0.0011446960633755066</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -1567,7 +1567,7 @@
         <v>0.023105528556228615</v>
       </c>
       <c r="B70">
-        <v>0.00097137387262685672</v>
+        <v>0.001033745656401418</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -1575,7 +1575,7 @@
         <v>0.021180067843209565</v>
       </c>
       <c r="B71">
-        <v>0.00086204705772575236</v>
+        <v>0.00092130862407119611</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -1583,7 +1583,7 @@
         <v>0.019254607130190511</v>
       </c>
       <c r="B72">
-        <v>0.00074867034307828269</v>
+        <v>0.00080445011825621793</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -1591,7 +1591,7 @@
         <v>0.017329146417171461</v>
       </c>
       <c r="B73">
-        <v>0.00062635577129686751</v>
+        <v>0.00067828030813625964</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -1599,7 +1599,7 @@
         <v>0.01540368570415241</v>
       </c>
       <c r="B74">
-        <v>0.00049707872281375533</v>
+        <v>0.00054477242378640821</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -1607,7 +1607,7 @@
         <v>0.01347822499113336</v>
       </c>
       <c r="B75">
-        <v>0.00036456713258724597</v>
+        <v>0.00040765210837625528</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -1615,7 +1615,7 @@
         <v>0.011552764278114308</v>
       </c>
       <c r="B76">
-        <v>0.00023269581586001287</v>
+        <v>0.00027079159655810244</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1623,7 +1623,7 @@
         <v>0.0096273035650952556</v>
       </c>
       <c r="B77">
-        <v>0.00010504846708552141</v>
+        <v>0.00013777185205114198</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1631,7 +1631,7 @@
         <v>0.0077018428520762051</v>
       </c>
       <c r="B78">
-        <v>-1.6102582723968355E-05</v>
+        <v>1.0862163359421065E-05</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1639,7 +1639,7 @@
         <v>0.0057763821390571539</v>
       </c>
       <c r="B79">
-        <v>-0.00012686142039731256</v>
+        <v>-0.00010604474172286713</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1647,7 +1647,7 @@
         <v>0.0038509214260381026</v>
       </c>
       <c r="B80">
-        <v>-0.00022036948560764667</v>
+        <v>-0.00020609377739379075</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1655,7 +1655,7 @@
         <v>0.0019254607130190513</v>
       </c>
       <c r="B81">
-        <v>-0.00027972994274724127</v>
+        <v>-0.00027239181072425295</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1663,7 +1663,7 @@
         <v>0</v>
       </c>
       <c r="B82">
-        <v>-6.8406106131357487E-17</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1681,7 +1681,7 @@
         <v>0</v>
       </c>
       <c r="B1">
-        <v>0</v>
+        <v>7.6610266448655455E-17</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -1689,7 +1689,7 @@
         <v>0.0021563872964432446</v>
       </c>
       <c r="B2">
-        <v>0.00063674781921123434</v>
+        <v>0.00064864752465335952</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1697,7 +1697,7 @@
         <v>0.0043127745928864892</v>
       </c>
       <c r="B3">
-        <v>0.00096776987996669884</v>
+        <v>0.00099094926626408443</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1705,7 +1705,7 @@
         <v>0.0064691618893297342</v>
       </c>
       <c r="B4">
-        <v>0.0012492513713972255</v>
+        <v>0.0012830919710361051</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1713,7 +1713,7 @@
         <v>0.0086255491857729783</v>
       </c>
       <c r="B5">
-        <v>0.0014954304755400527</v>
+        <v>0.001539315290557508</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1721,7 +1721,7 @@
         <v>0.010781936482216223</v>
       </c>
       <c r="B6">
-        <v>0.0017121110775303219</v>
+        <v>0.0017654244974729279</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1729,7 +1729,7 @@
         <v>0.012938323778659468</v>
       </c>
       <c r="B7">
-        <v>0.0019026051890207718</v>
+        <v>0.0019647328848664794</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1737,7 +1737,7 @@
         <v>0.015094711075102713</v>
       </c>
       <c r="B8">
-        <v>0.0020688593973908122</v>
+        <v>0.0021391882682427594</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1745,7 +1745,7 @@
         <v>0.017251098371545957</v>
       </c>
       <c r="B9">
-        <v>0.0022139180410161463</v>
+        <v>0.0022918360964460779</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1753,7 +1753,7 @@
         <v>0.0194074856679892</v>
       </c>
       <c r="B10">
-        <v>0.0023410681730492446</v>
+        <v>0.002425964475592107</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1761,7 +1761,7 @@
         <v>0.021563872964432445</v>
       </c>
       <c r="B11">
-        <v>0.002453469954753356</v>
+        <v>0.0025447345075422633</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1769,7 +1769,7 @@
         <v>0.023720260260875693</v>
       </c>
       <c r="B12">
-        <v>0.0025528097544143678</v>
+        <v>0.0026498334455725791</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1777,7 +1777,7 @@
         <v>0.025876647557318937</v>
       </c>
       <c r="B13">
-        <v>0.0026350056602979376</v>
+        <v>0.002737180152871809</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1785,7 +1785,7 @@
         <v>0.028033034853762181</v>
       </c>
       <c r="B14">
-        <v>0.0026976159570874553</v>
+        <v>0.0028043336317864643</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1793,7 +1793,7 @@
         <v>0.030189422150205425</v>
       </c>
       <c r="B15">
-        <v>0.0027505279951574712</v>
+        <v>0.0028611818313813648</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1801,7 +1801,7 @@
         <v>0.032345809446648666</v>
       </c>
       <c r="B16">
-        <v>0.0028028104044859345</v>
+        <v>0.0029167939303047412</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1809,7 +1809,7 @@
         <v>0.034502196743091913</v>
       </c>
       <c r="B17">
-        <v>0.0028479278677732292</v>
+        <v>0.0029646350788201767</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1817,7 +1817,7 @@
         <v>0.036658584039535161</v>
       </c>
       <c r="B18">
-        <v>0.002877441326625678</v>
+        <v>0.0029962666201791294</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1825,7 +1825,7 @@
         <v>0.0388149713359784</v>
       </c>
       <c r="B19">
-        <v>0.002890900705550922</v>
+        <v>0.0030112386979692062</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1833,7 +1833,7 @@
         <v>0.040971358632421649</v>
       </c>
       <c r="B20">
-        <v>0.0028898531747819324</v>
+        <v>0.0030110986558620546</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1841,7 +1841,7 @@
         <v>0.04312774592886489</v>
       </c>
       <c r="B21">
-        <v>0.0028758459045516781</v>
+        <v>0.0029973938375293181</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1849,7 +1849,7 @@
         <v>0.045284133225308137</v>
       </c>
       <c r="B22">
-        <v>0.0028501506485419741</v>
+        <v>0.002971396113362564</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1857,7 +1857,7 @@
         <v>0.047440520521751385</v>
       </c>
       <c r="B23">
-        <v>0.0028129374942300052</v>
+        <v>0.0029332754606330373</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1865,7 +1865,7 @@
         <v>0.049596907818194626</v>
       </c>
       <c r="B24">
-        <v>0.0027641011125418007</v>
+        <v>0.0028829263833319062</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1873,7 +1873,7 @@
         <v>0.051753295114637873</v>
       </c>
       <c r="B25">
-        <v>0.0027035361744033896</v>
+        <v>0.0028202433854503362</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1881,7 +1881,7 @@
         <v>0.053909682411081114</v>
       </c>
       <c r="B26">
-        <v>0.0026310919216216422</v>
+        <v>0.002745075487180637</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1889,7 +1889,7 @@
         <v>0.056066069707524362</v>
       </c>
       <c r="B27">
-        <v>0.0025464358795268048</v>
+        <v>0.0026570897735196828</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1897,7 +1897,7 @@
         <v>0.0582224570039676</v>
       </c>
       <c r="B28">
-        <v>0.0024491901443299637</v>
+        <v>0.0025559078456654912</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1905,7 +1905,7 @@
         <v>0.06037884430041085</v>
       </c>
       <c r="B29">
-        <v>0.0023389768122422079</v>
+        <v>0.0024411513048160794</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1913,7 +1913,7 @@
         <v>0.0625352315968541</v>
       </c>
       <c r="B30">
-        <v>0.00221562306687053</v>
+        <v>0.0023126467842404814</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1921,7 +1921,7 @@
         <v>0.064691618893297331</v>
       </c>
       <c r="B31">
-        <v>0.0020797764414055438</v>
+        <v>0.0021710410454917994</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1929,7 +1929,7 @@
         <v>0.066848006189740586</v>
       </c>
       <c r="B32">
-        <v>0.0019322895564337689</v>
+        <v>0.002017185882194151</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1937,7 +1937,7 @@
         <v>0.069004393486183827</v>
       </c>
       <c r="B33">
-        <v>0.0017740150325417242</v>
+        <v>0.0018519330879716558</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1945,7 +1945,7 @@
         <v>0.071160780782627067</v>
       </c>
       <c r="B34">
-        <v>0.0016054739521999973</v>
+        <v>0.0016758028605231741</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1953,7 +1953,7 @@
         <v>0.073317168079070322</v>
       </c>
       <c r="B35">
-        <v>0.0014258612454154478</v>
+        <v>0.0014879890138465332</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1961,7 +1961,7 @@
         <v>0.075473555375513562</v>
       </c>
       <c r="B36">
-        <v>0.0012340403040790042</v>
+        <v>0.0012873537660143019</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1969,7 +1969,7 @@
         <v>0.0776299426719568</v>
       </c>
       <c r="B37">
-        <v>0.0010288745200815925</v>
+        <v>0.0010727593350990479</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1977,7 +1977,7 @@
         <v>0.079786329968400044</v>
       </c>
       <c r="B38">
-        <v>0.00080841430413756553</v>
+        <v>0.000842254905703667</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1985,7 +1985,7 @@
         <v>0.0819427172648433</v>
       </c>
       <c r="B39">
-        <v>0.000567458142254974</v>
+        <v>0.00059063752855235963</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1993,7 +1993,7 @@
         <v>0.084099104561286539</v>
       </c>
       <c r="B40">
-        <v>0.00029999153926529328</v>
+        <v>0.00031189122089965324</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2001,7 +2001,7 @@
         <v>0.08625549185772978</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>7.6610266448655455E-17</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -2009,7 +2009,7 @@
         <v>0.08625549185772978</v>
       </c>
       <c r="B42">
-        <v>9.3518391660956366E-21</v>
+        <v>7.6610266448655455E-17</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -2017,7 +2017,7 @@
         <v>0.084099104561286539</v>
       </c>
       <c r="B43">
-        <v>1.6067948666354339E-05</v>
+        <v>2.796763030071433E-05</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2025,7 +2025,7 @@
         <v>0.0819427172648433</v>
       </c>
       <c r="B44">
-        <v>4.837259225515724E-05</v>
+        <v>7.1551978552542822E-05</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2033,7 +2033,7 @@
         <v>0.079786329968400044</v>
       </c>
       <c r="B45">
-        <v>9.0911634268263641E-05</v>
+        <v>0.00012475223583436498</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2041,7 +2041,7 @@
         <v>0.0776299426719568</v>
       </c>
       <c r="B46">
-        <v>0.00013768277820752845</v>
+        <v>0.00018156759322498386</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2049,7 +2049,7 @@
         <v>0.075473555375513562</v>
       </c>
       <c r="B47">
-        <v>0.00018349628505154528</v>
+        <v>0.00023680974698684292</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2057,7 +2057,7 @@
         <v>0.073317168079070322</v>
       </c>
       <c r="B48">
-        <v>0.00022641264568586215</v>
+        <v>0.00028854041411694733</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -2065,7 +2065,7 @@
         <v>0.071160780782627067</v>
       </c>
       <c r="B49">
-        <v>0.00026530490847276642</v>
+        <v>0.00033563381679594328</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -2073,7 +2073,7 @@
         <v>0.069004393486183827</v>
       </c>
       <c r="B50">
-        <v>0.00029904612177454474</v>
+        <v>0.00037696417720447638</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -2081,7 +2081,7 @@
         <v>0.066848006189740586</v>
       </c>
       <c r="B51">
-        <v>0.00032684039974534838</v>
+        <v>0.00041173672550573053</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -2089,7 +2089,7 @@
         <v>0.064691618893297331</v>
       </c>
       <c r="B52">
-        <v>0.00034921611970678627</v>
+        <v>0.00044048072379304149</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -2097,7 +2097,7 @@
         <v>0.0625352315968541</v>
       </c>
       <c r="B53">
-        <v>0.00036703272477233166</v>
+        <v>0.00046405644214228309</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -2105,7 +2105,7 @@
         <v>0.06037884430041085</v>
       </c>
       <c r="B54">
-        <v>0.000381149658055458</v>
+        <v>0.00048332415062932947</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -2113,7 +2113,7 @@
         <v>0.0582224570039676</v>
       </c>
       <c r="B55">
-        <v>0.00039222082000991873</v>
+        <v>0.00049893852134544618</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -2121,7 +2121,7 @@
         <v>0.056066069707524362</v>
       </c>
       <c r="B56">
-        <v>0.00040007794045058865</v>
+        <v>0.00051073183444346707</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -2129,7 +2129,7 @@
         <v>0.053909682411081114</v>
       </c>
       <c r="B57">
-        <v>0.0004043472065326226</v>
+        <v>0.00051833077209161753</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -2137,7 +2137,7 @@
         <v>0.051753295114637873</v>
       </c>
       <c r="B58">
-        <v>0.00040465480541117558</v>
+        <v>0.0005213620164581231</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -2145,7 +2145,7 @@
         <v>0.049596907818194626</v>
       </c>
       <c r="B59">
-        <v>0.00040067190167716654</v>
+        <v>0.000519497172467272</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -2153,7 +2153,7 @@
         <v>0.047440520521751385</v>
       </c>
       <c r="B60">
-        <v>0.00039224956966457024</v>
+        <v>0.00051258753606760242</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -2161,7 +2161,7 @@
         <v>0.045284133225308137</v>
       </c>
       <c r="B61">
-        <v>0.00037928386114312546</v>
+        <v>0.0005005293259637151</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -2169,7 +2169,7 @@
         <v>0.04312774592886489</v>
       </c>
       <c r="B62">
-        <v>0.000361670827882571</v>
+        <v>0.000483218760860211</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -2177,7 +2177,7 @@
         <v>0.040971358632421649</v>
       </c>
       <c r="B63">
-        <v>0.00033958146898385369</v>
+        <v>0.0004608269500639759</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -2185,7 +2185,7 @@
         <v>0.0388149713359784</v>
       </c>
       <c r="B64">
-        <v>0.00031428657287275129</v>
+        <v>0.0004346245652910356</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -2193,7 +2193,7 @@
         <v>0.036658584039535161</v>
       </c>
       <c r="B65">
-        <v>0.00028733187530625011</v>
+        <v>0.00040615716885970121</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -2201,7 +2201,7 @@
         <v>0.034502196743091913</v>
       </c>
       <c r="B66">
-        <v>0.00026026311204133595</v>
+        <v>0.00037697032308828347</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -2209,7 +2209,7 @@
         <v>0.032345809446648666</v>
       </c>
       <c r="B67">
-        <v>0.00023262839594183644</v>
+        <v>0.00034661192176064305</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -2217,7 +2217,7 @@
         <v>0.030189422150205425</v>
       </c>
       <c r="B68">
-        <v>0.00019598534829894622</v>
+        <v>0.00030663918452283949</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -2225,7 +2225,7 @@
         <v>0.028033034853762181</v>
       </c>
       <c r="B69">
-        <v>0.00014379478726377513</v>
+        <v>0.00025051246196278458</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -2233,7 +2233,7 @@
         <v>0.025876647557318937</v>
       </c>
       <c r="B70">
-        <v>8.5120809999729655E-05</v>
+        <v>0.00018729530257360113</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -2241,7 +2241,7 @@
         <v>0.023720260260875693</v>
       </c>
       <c r="B71">
-        <v>2.9845822199984731E-05</v>
+        <v>0.0001268695133581959</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -2249,7 +2249,7 @@
         <v>0.021563872964432445</v>
       </c>
       <c r="B72">
-        <v>-2.4477815335504657E-05</v>
+        <v>6.6786737453402537E-05</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -2257,7 +2257,7 @@
         <v>0.0194074856679892</v>
       </c>
       <c r="B73">
-        <v>-8.1938408704183616E-05</v>
+        <v>2.9578938386790189E-06</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -2265,7 +2265,7 @@
         <v>0.017251098371545957</v>
       </c>
       <c r="B74">
-        <v>-0.00014085688669987717</v>
+        <v>-6.29388312699455E-05</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -2273,7 +2273,7 @@
         <v>0.015094711075102713</v>
       </c>
       <c r="B75">
-        <v>-0.00019808084045352722</v>
+        <v>-0.00012775196960157978</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -2281,7 +2281,7 @@
         <v>0.012938323778659468</v>
       </c>
       <c r="B76">
-        <v>-0.00025033188774816357</v>
+        <v>-0.00018820419190245584</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -2289,7 +2289,7 @@
         <v>0.010781936482216223</v>
       </c>
       <c r="B77">
-        <v>-0.00029457483009312914</v>
+        <v>-0.00024126141015052302</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -2297,7 +2297,7 @@
         <v>0.0086255491857729783</v>
       </c>
       <c r="B78">
-        <v>-0.00032887317725093174</v>
+        <v>-0.00028498836223347636</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -2305,7 +2305,7 @@
         <v>0.0064691618893297342</v>
       </c>
       <c r="B79">
-        <v>-0.00034992544764508447</v>
+        <v>-0.00031608484800620481</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -2313,7 +2313,7 @@
         <v>0.0043127745928864892</v>
       </c>
       <c r="B80">
-        <v>-0.00035193914545656634</v>
+        <v>-0.0003287597591591807</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -2321,7 +2321,7 @@
         <v>0.0021563872964432446</v>
       </c>
       <c r="B81">
-        <v>-0.00032068814040956604</v>
+        <v>-0.00030878843496744097</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -2329,7 +2329,7 @@
         <v>0</v>
       </c>
       <c r="B82">
-        <v>0</v>
+        <v>7.6610266448655455E-17</v>
       </c>
     </row>
   </sheetData>
